--- a/hasil_preprocessing.xlsx
+++ b/hasil_preprocessing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trial\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Dokumen\Temu Kembali Informasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1775E896-3832-4436-9D46-D3A510E29E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6809A25-FE22-46E0-AFC7-3F16D1F1B127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hasil TF-IDF Weighting" sheetId="9" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="Inverted Index Matrix" sheetId="1" r:id="rId5"/>
     <sheet name="Posting List" sheetId="2" r:id="rId6"/>
     <sheet name="Index Per Dokumen" sheetId="3" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -2688,11 +2687,11 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3005,7 +3004,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:171" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>831</v>
       </c>
       <c r="B1" s="17"/>
@@ -29465,7 +29464,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>828</v>
       </c>
       <c r="B1" s="17"/>
@@ -30362,7 +30361,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>751</v>
       </c>
       <c r="B1" s="17"/>
@@ -31411,7 +31410,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>601</v>
       </c>
       <c r="B1" s="17"/>
@@ -32304,7 +32303,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:171" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="17"/>
@@ -58765,7 +58764,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>223</v>
       </c>
       <c r="B1" s="17"/>
@@ -62214,7 +62213,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>447</v>
       </c>
       <c r="B1" s="17"/>
@@ -63095,13 +63094,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C351C8F-6174-410B-ADDA-FD1C651430A0}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>